--- a/ksoft/docs/records/Expense_Type_Records.xlsx
+++ b/ksoft/docs/records/Expense_Type_Records.xlsx
@@ -2886,13 +2886,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5669B31F-55B1-46EA-80F5-93956289F834}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B366E34-5492-49C6-9207-1F7562EDA8BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF2DAF0E-D12E-4787-95DC-D32CB98F550B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{049441EF-1E6E-479E-A17B-4250130DC120}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DDDB629-A8D2-4C70-9E86-84CE9F0DC390}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17CE10D-73C0-4CE9-A47F-73ED2AAEEC56}"/>
 </file>
--- a/ksoft/docs/records/Expense_Type_Records.xlsx
+++ b/ksoft/docs/records/Expense_Type_Records.xlsx
@@ -2886,13 +2886,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B366E34-5492-49C6-9207-1F7562EDA8BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5669B31F-55B1-46EA-80F5-93956289F834}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{049441EF-1E6E-479E-A17B-4250130DC120}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF2DAF0E-D12E-4787-95DC-D32CB98F550B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17CE10D-73C0-4CE9-A47F-73ED2AAEEC56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DDDB629-A8D2-4C70-9E86-84CE9F0DC390}"/>
 </file>